--- a/Lab Assignemnt 2/LAB2_earthquake.xlsx
+++ b/Lab Assignemnt 2/LAB2_earthquake.xlsx
@@ -5,17 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9243a5fe3e20cb94/Desktop/DAV Lab-Assignments/lab-assignment-2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DAV Lab Assignments\Lab Assignemnt 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="11_7648CB33795048EFDEA3B44F7E99B51C5A00CFF6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA2AC0FF-2F2C-4275-ABF1-28DAD7130A97}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE51205-179E-49C1-9958-67C099F1D618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DS" sheetId="1" r:id="rId1"/>
     <sheet name="TASK" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">TASK!$A$32:$A$37</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">TASK!$B$31</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">TASK!$B$32:$B$37</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">TASK!$A$32:$A$37</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">TASK!$B$31</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">TASK!$B$32:$B$37</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -5007,7 +5015,7 @@
       <name val="Arimo"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5036,6 +5044,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEFEFEF"/>
         <bgColor rgb="FFEFEFEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor rgb="FF00FFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -5079,7 +5093,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -5109,6 +5123,12 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5147,13 +5167,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
                   </a:schemeClr>
                 </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
@@ -5161,13 +5187,8 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-IN"/>
-              <a:t>VALUE</a:t>
+              <a:t>VALUE RANGE</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="en-IN" baseline="0"/>
-              <a:t> RANGE</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-IN"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -5184,19 +5205,25 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
                 </a:schemeClr>
               </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-IN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -5261,13 +5288,42 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
             <a:sp3d/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -5333,13 +5389,42 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
             <a:sp3d/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -5405,13 +5490,42 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent3">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent3">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
             <a:sp3d/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -5477,13 +5591,42 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4"/>
-            </a:solidFill>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent4">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent4">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
             <a:sp3d/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -5573,9 +5716,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -5604,9 +5746,9 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -5632,9 +5774,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -5673,9 +5814,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -5714,9 +5854,8 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -5740,17 +5879,28 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
@@ -5793,11 +5943,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -5807,13 +5957,8 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>COUNT BY ALERT</a:t>
+              <a:t>COUNT BY ALERT LEVEL</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> LEVEL</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -5830,11 +5975,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -5848,7 +5993,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:view3D>
-      <c:rotX val="30"/>
+      <c:rotX val="50"/>
       <c:rotY val="0"/>
       <c:depthPercent val="100"/>
       <c:rAngAx val="0"/>
@@ -5921,18 +6066,23 @@
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:ln w="25400">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
-              <a:sp3d contourW="25400">
-                <a:contourClr>
-                  <a:schemeClr val="lt1"/>
-                </a:contourClr>
-              </a:sp3d>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-FF7D-455F-A1A5-C9AAF003B008}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -5941,18 +6091,23 @@
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
-              <a:ln w="25400">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
-              <a:sp3d contourW="25400">
-                <a:contourClr>
-                  <a:schemeClr val="lt1"/>
-                </a:contourClr>
-              </a:sp3d>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-FF7D-455F-A1A5-C9AAF003B008}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -5961,18 +6116,23 @@
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
-              <a:ln w="25400">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
-              <a:sp3d contourW="25400">
-                <a:contourClr>
-                  <a:schemeClr val="lt1"/>
-                </a:contourClr>
-              </a:sp3d>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-FF7D-455F-A1A5-C9AAF003B008}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -5981,18 +6141,23 @@
               <a:solidFill>
                 <a:schemeClr val="accent4"/>
               </a:solidFill>
-              <a:ln w="25400">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
-              <a:sp3d contourW="25400">
-                <a:contourClr>
-                  <a:schemeClr val="lt1"/>
-                </a:contourClr>
-              </a:sp3d>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-FF7D-455F-A1A5-C9AAF003B008}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -6001,18 +6166,23 @@
               <a:solidFill>
                 <a:schemeClr val="accent5"/>
               </a:solidFill>
-              <a:ln w="25400">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
-              <a:sp3d contourW="25400">
-                <a:contourClr>
-                  <a:schemeClr val="lt1"/>
-                </a:contourClr>
-              </a:sp3d>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-FF7D-455F-A1A5-C9AAF003B008}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -6021,19 +6191,95 @@
               <a:solidFill>
                 <a:schemeClr val="accent6"/>
               </a:solidFill>
-              <a:ln w="25400">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
-              <a:sp3d contourW="25400">
-                <a:contourClr>
-                  <a:schemeClr val="lt1"/>
-                </a:contourClr>
-              </a:sp3d>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-FF7D-455F-A1A5-C9AAF003B008}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:pattFill prst="pct75">
+                <a:fgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>TASK!$D$19:$D$24</c:f>
@@ -6094,11 +6340,12 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
+          <c:showPercent val="1"/>
           <c:showBubbleSize val="0"/>
           <c:showLeaderLines val="1"/>
         </c:dLbls>
@@ -6112,10 +6359,25 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="2.9730971128608903E-2"/>
+          <c:y val="0.52712780694079908"/>
+          <c:w val="0.28971347331583552"/>
+          <c:h val="0.46875328083989504"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
-        <a:noFill/>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="39000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -6128,9 +6390,9 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -6154,14 +6416,30 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="39000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:round/>
@@ -6207,443 +6485,10 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-IN"/>
-              <a:t>MAGNITUDE</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-IN" baseline="0"/>
-              <a:t> BAND DISTRIBUTION</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-IN"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:view3D>
-      <c:rotX val="15"/>
-      <c:rotY val="20"/>
-      <c:depthPercent val="100"/>
-      <c:rAngAx val="0"/>
-    </c:view3D>
-    <c:floor>
-      <c:thickness val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="tx1">
-              <a:lumMod val="15000"/>
-              <a:lumOff val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:round/>
-        </a:ln>
-        <a:effectLst/>
-        <a:sp3d contourW="9525">
-          <a:contourClr>
-            <a:schemeClr val="tx1">
-              <a:lumMod val="15000"/>
-              <a:lumOff val="85000"/>
-            </a:schemeClr>
-          </a:contourClr>
-        </a:sp3d>
-      </c:spPr>
-    </c:floor>
-    <c:sideWall>
-      <c:thickness val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
-      </c:spPr>
-    </c:sideWall>
-    <c:backWall>
-      <c:thickness val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
-      </c:spPr>
-    </c:backWall>
-    <c:plotArea>
-      <c:layout/>
-      <c:area3DChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>TASK!$B$31</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>COUNT</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-            <a:sp3d/>
-          </c:spPr>
-          <c:cat>
-            <c:strRef>
-              <c:f>TASK!$A$32:$A$37</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>6.5-6.9</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>7.0-7.4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7.5-7.9</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.0-8.4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8.5-8.9</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>9.0-9.4</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>TASK!$B$32:$B$37</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>627</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>229</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>112</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CAC4-4C7F-934B-30C861EAAB11}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="110813408"/>
-        <c:axId val="13254160"/>
-        <c:axId val="116233040"/>
-      </c:area3DChart>
-      <c:catAx>
-        <c:axId val="110813408"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="13254160"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="13254160"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="110813408"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:serAx>
-        <c:axId val="116233040"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="13254160"/>
-        <c:crosses val="autoZero"/>
-      </c:serAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -6671,11 +6516,10 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -6708,27 +6552,41 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="22225" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="3"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:glow rad="63500">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="175000"/>
+                    <a:alpha val="25000"/>
+                  </a:schemeClr>
+                </a:glow>
+              </a:effectLst>
             </c:spPr>
           </c:marker>
           <c:xVal>
@@ -6837,9 +6695,10 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -6854,9 +6713,8 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -6870,9 +6728,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -6898,9 +6755,10 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -6916,9 +6774,8 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -6932,9 +6789,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -6970,11 +6826,14 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
+        <a:schemeClr val="dk1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -7001,7 +6860,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7071,7 +6930,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-IN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -7465,6 +7324,91 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.0</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.2</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>MAGNITUDE BAND DISTRIBUTION</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike" spc="100" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF">
+                  <a:lumMod val="95000"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:rPr>
+            <a:t>MAGNITUDE BAND DISTRIBUTION</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="clusteredColumn" uniqueId="{00000000-26C6-4A7F-B974-8787DCFC45AD}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.1</cx:f>
+              <cx:v>COUNT</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:aggregation/>
+          </cx:layoutPr>
+          <cx:axisId val="1"/>
+        </cx:series>
+        <cx:series layoutId="paretoLine" ownerIdx="0" uniqueId="{6E237721-17DE-46B5-8C03-AB5CA6E51CF1}">
+          <cx:axisId val="2"/>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="0"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="2">
+        <cx:valScaling max="1" min="0"/>
+        <cx:units unit="percentage"/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -7666,51 +7610,58 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="294">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr/>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:chartArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
     </cs:spPr>
     <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
@@ -7719,9 +7670,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -7740,14 +7690,6 @@
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -7756,20 +7698,20 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
@@ -7778,13 +7720,13 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="34925" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -7796,10 +7738,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
@@ -7808,16 +7750,17 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
@@ -7835,21 +7778,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -7868,14 +7808,13 @@
           <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -7887,14 +7826,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -7908,7 +7847,563 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr/>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="264">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
@@ -7922,14 +8417,583 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
       <a:ln>
         <a:noFill/>
       </a:ln>
     </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="245">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="3"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
@@ -7941,9 +9005,10 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="75000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -7960,9 +9025,10 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -7974,14 +9040,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="lt1">
             <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -7993,14 +9058,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -8012,27 +9076,26 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea3D>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -8040,9 +9103,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -8052,14 +9114,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -8071,12 +9132,11 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -8085,14 +9145,15 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="25400" cap="rnd">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -8101,9 +9162,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -8113,17 +9173,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -8135,550 +9196,35 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr/>
   </cs:valueAxis>
   <cs:wall>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="262">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="276">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -9199,77 +9745,82 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="370">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:chartArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="1000"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
     <cs:lnRef idx="0"/>
@@ -9294,42 +9845,80 @@
         </a:solidFill>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
       <a:spAutoFit/>
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr">
+              <a:satMod val="103000"/>
+              <a:lumMod val="102000"/>
+              <a:tint val="94000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="50000">
+            <a:schemeClr val="phClr">
+              <a:satMod val="110000"/>
+              <a:lumMod val="100000"/>
+              <a:shade val="100000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="99000"/>
+              <a:satMod val="120000"/>
+              <a:shade val="78000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="34925" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -9338,25 +9927,26 @@
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
@@ -9364,10 +9954,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -9380,24 +9970,21 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900"/>
   </cs:dataTable>
   <cs:downBar>
     <cs:lnRef idx="0"/>
@@ -9413,14 +10000,13 @@
           <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -9432,14 +10018,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -9448,14 +10034,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9467,28 +10052,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9500,17 +10079,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+            <a:lumOff val="10000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -9522,14 +10101,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -9538,17 +10117,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -9557,27 +10135,26 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea3D>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -9585,27 +10162,34 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
   </cs:seriesAxis>
   <cs:seriesLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525" cap="flat">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
+          <a:srgbClr val="D9D9D9"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
@@ -9616,12 +10200,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1600" b="1" spc="100">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -9630,14 +10221,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
+        <a:prstDash val="sysDash"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -9646,12 +10237,11 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900"/>
   </cs:trendlineLabel>
   <cs:upBar>
     <cs:lnRef idx="0"/>
@@ -9664,14 +10254,13 @@
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -9680,558 +10269,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900"/>
   </cs:valueAxis>
   <cs:wall>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="276">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -10313,42 +10363,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>129540</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>102870</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>541020</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>41910</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="9" name="Chart 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FE326DB-CFB0-9B4E-4034-EFEF0B0F8426}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>118110</xdr:rowOff>
@@ -10376,7 +10390,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -10412,10 +10426,88 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>586740</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Chart 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F3D8F60-A779-A622-ACD1-F3D31522F3A5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7223760" y="5665470"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -64901,19 +64993,19 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="20" t="s">
         <v>1595</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="19" t="s">
         <v>1596</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="19" t="s">
         <v>1597</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="19" t="s">
         <v>1598</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="19" t="s">
         <v>1599</v>
       </c>
     </row>
@@ -65015,16 +65107,16 @@
       <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="19" t="s">
         <v>1603</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="19" t="s">
         <v>1604</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="19" t="s">
         <v>1605</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="19" t="s">
         <v>1604</v>
       </c>
     </row>
@@ -65172,18 +65264,18 @@
       </c>
       <c r="B30" s="18"/>
       <c r="C30" s="18"/>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="19" t="s">
         <v>1623</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="19" t="s">
         <v>1604</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="19" t="s">
         <v>1624</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="19" t="s">
         <v>1604</v>
       </c>
       <c r="D31" s="1">
